--- a/02_加值成品/九上/九上3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上3-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上3-2 力學能　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上3-2 力學能　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>物體運動具有的能量是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>質量與速率</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>動能</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>力學能</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>運動</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>因高度具有的能量是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>重力位能</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>位能</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>高度</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>動能與什麼有關？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>質量與高度</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>質量與速率</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>重力位能</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>兩者</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>位能與什麼有關？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>重力位能</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>最小</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>守恆</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>質量與高度</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>兩者</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>動能加位能稱？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>力學能</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>質量與速率</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>總和</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>速率越快動能？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>力學能</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>質量與速率</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>正比</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>高度越高位能？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>質量與高度</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>力學能</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>質量與速率</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>正比</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>不計摩擦力學能？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>力學能</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>加倍</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>不變</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>物體因運動而具有的能量是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>質量與速率</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>加倍</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>動能</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>運動</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>物體因高度而具有的能量是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>動能減位能增</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>質量與高度</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>重力位能</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>位能</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>高度</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上3-2 力學能　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上3-2 力學能　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>自由落體下落時位能如何？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>減少</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>質量與速率</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>力學能</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>重力位能</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>轉動能</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>自由落體下落時動能如何？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>守恆</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>動能減位能增</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>增加</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>位能轉來</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>物體最高點動能通常？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>最小</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>力學能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>加倍</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>速率最慢</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>物體最低點位能通常？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>加倍</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>最小</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>質量與速率</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>高度低</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>單擺最低點什麼能最大？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>加倍</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>動能</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>最小</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>力學能</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>速率最快</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>雲霄飛車頂端主要具有？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>位能</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>力學能</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>高處</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>質量加倍高度不變位能？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>重力位能</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>守恆</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>加倍</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>正比</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>有摩擦時力學能會？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>減少</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>重力位能</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>轉熱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>物體越快動能越？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>最小</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>質量與速率</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>重力位能</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>動能</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>雲霄飛車最高點主要具有哪種能？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>位能</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>重力位能</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>高處</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上3-2 力學能　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上3-2 力學能　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>自由落體過程用守恆說明能量變化？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>動能最大位能最小</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>重球(質量大)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>摩擦耗損力學能</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>位能減少等於動能增加,總量不變</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>單擺為何最低點最快最高點最慢？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>重球(質量大)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>位能與動能互換,低點動能最大</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>位能減少等於動能增加,總量不變</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>重力位能→動能→電能</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>雲霄飛車不計摩擦頂端與底部力學能關係？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>相等</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>拋球上升到最高點動能位能如何？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>動能最大位能最小</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>重力位能→動能→電能</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>動能為零位能最大</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>摩擦耗損力學能</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>極值</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>水力發電將水的什麼能轉成電能？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>重球(質量大)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>位能與動能互換,低點動能最大</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>重力位能→動能→電能</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>摩擦耗損力學能</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>為何實際力學能會逐漸減少？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>重球(質量大)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>摩擦耗損力學能</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>動能為零位能最大</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>摩擦與空氣阻力轉成熱</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>耗散</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>同高度落下重球與輕球誰位能大？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>動能為零位能最大</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>動能最大位能最小</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>重球(質量大)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>摩擦與空氣阻力轉成熱</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>質量</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>盪鞦韆越盪越低是因為？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>摩擦耗損力學能</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>動能最大位能最小</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>重力位能→動能→電能</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>位能與動能互換,低點動能最大</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>非守恆</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>自由落體到最低點時動能與位能？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>動能最大位能最小</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>摩擦與空氣阻力轉成熱</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>重球(質量大)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>重力位能→動能→電能</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>拋球上升過程動能與位能如何變？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>質量與高度</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>動能減位能增</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>位能</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>轉換</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上3-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>運動</t>
+          <t>運動：只要物體在動,就會具有這種因為運動而擁有的能量</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>高度</t>
+          <t>高度：物體因為位置比較高,而具有可以轉換成別種能量的能量</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>兩者</t>
+          <t>兩者：物體的質量越大、跑得越快,動能就會跟著越大</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>兩者</t>
+          <t>兩者：物體的質量越大、位置越高,重力位能就會跟著越大</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>總和</t>
+          <t>總和：把動能和位能加在一起,合稱為這個物體的力學能</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>正比</t>
+          <t>正比：物體移動得越快,它所具有的動能就越大</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>正比</t>
+          <t>正比：物體所在的位置越高,它所具有的重力位能就越大</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>不變</t>
+          <t>不變：如果沒有摩擦力偷走能量,動能加位能的總和會保持固定</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>運動</t>
+          <t>運動：物體只要在運動,就具有動能,速度越快、質量越大,動能就越大</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>高度</t>
+          <t>高度：物體因為所在的高度而具有能量,叫做重力位能,位置越高位能越大</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>轉動能</t>
+          <t>轉動能：物體越落越低,高度變小,重力位能也跟著慢慢減少</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>位能轉來</t>
+          <t>位能轉來：減少的位能轉換成動能,所以物體越落越快,動能越來越大</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>速率最慢</t>
+          <t>速率最慢：到達最高點時物體速度最慢甚至瞬間為零,所以動能最小</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>高度低</t>
+          <t>高度低：在最低的位置高度接近零,所以重力位能也最小</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>速率最快</t>
+          <t>速率最快：單擺盪到最低點時速度最快,所以動能在那一瞬間最大</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>高處</t>
+          <t>高處：在最高的軌道上,雲霄飛車速度慢但位置高,主要能量是位能</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>正比</t>
+          <t>正比：高度沒有改變,只要質量變成兩倍,位能也會跟著變成兩倍</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>轉熱</t>
+          <t>轉熱：摩擦力會把一部分力學能轉變成熱能散失掉,所以力學能會減少</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>動能</t>
+          <t>動能：動能與速度的平方成正比,物體運動得越快,動能就越大</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>高處</t>
+          <t>高處：雲霄飛車在最高點時速度通常最慢、位置最高,這時能量主要以重力位能的形式存在</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：位能減少的量剛好等於動能增加的量,兩者加起來的總力學能維持不變</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：擺盪過程位能和動能不斷互相轉換,位能全部變動能時速度最快,反之最慢</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：沒有摩擦損耗能量的話,不管在哪個高度,力學能的總量都會保持相同</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>極值</t>
+          <t>極值：到最高點瞬間速度變成零所以動能為零,而位置最高所以位能達到最大值</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：高處的水先靠位能落下轉成動能沖擊水輪機,再由發電機轉成電能</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>耗散</t>
+          <t>耗散：現實中摩擦力和空氣阻力會把部分力學能轉變成熱能,所以力學能不能完全守恆</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>質量</t>
+          <t>質量：兩球高度一樣,但重球質量比輕球大,所以重球的重力位能比較大</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>非守恆</t>
+          <t>非守恆：空氣阻力和支點摩擦不斷消耗力學能,所以鞦韆會越盪越低越慢</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：自由落體過程中總機械能守恆,位能不斷轉成動能,到最低點時位能幾乎全部轉為動能,動能最大</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：球往上飛時速度漸漸變慢、高度漸漸增加,動能不斷轉換成位能,所以動能減少、位能增加</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上3-2_三種難度測驗卷.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>質量與速率</t>
+          <t>重力位能</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>減少</t>
+          <t>越大</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>力學能</t>
+          <t>質量與高度</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>位能</t>
+          <t>力學能</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>相等</t>
+          <t>動能</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>動能</t>
+          <t>質量與速率</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>力學能</t>
+          <t>動能</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>質量與速率</t>
+          <t>質量與高度</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>動能</t>
+          <t>動能減位能增</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>質量與高度</t>
+          <t>位能</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>力學能</t>
+          <t>質量與速率</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>質量與速率</t>
+          <t>動能</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -883,17 +883,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>加倍</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
           <t>質量與速率</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>越大</t>
-        </is>
-      </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>加倍</t>
+          <t>質量與高度</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>動能減位能增</t>
+          <t>力學能</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>質量與高度</t>
+          <t>減少</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>重力位能</t>
+          <t>最小</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>加倍</t>
+          <t>重力位能</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>最小</t>
+          <t>質量與高度</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>力學能</t>
+          <t>增加</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1244,17 +1244,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>力學能</t>
+          <t>大</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>動能</t>
+          <t>減少</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>增加</t>
+          <t>越大</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>最小</t>
+          <t>位能</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>質量與速率</t>
+          <t>相等</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>重力位能</t>
+          <t>動能減位能增</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>增加</t>
+          <t>最小</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>重力位能</t>
+          <t>大</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
+          <t>質量與速率</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>動能減位能增</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
           <t>質量與高度</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>動能減位能增</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>位能</t>
-        </is>
-      </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>減少</t>
+          <t>相等</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
